--- a/stories/arbres/TREE-EMO-005.xlsx
+++ b/stories/arbres/TREE-EMO-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le salon, Sara construisait une tour. La tour tombe. Un frère a bougé trop près. Le visage de Sara devient chaud. Maman est sur le canapé. Papa rentre des courses. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge roule trop loin. Sara est en colère. Voici le ballon rouge. La couverture est toute douce. Sara s'approche, sans courir. Papa n'est pas loin. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le ballon rouge.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2181,6 +2223,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2345,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Tom, après le ballon rouge. Une goutte de pluie sèche déjà. Tom reste à sa place. Sara aussi. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le ballon rouge et Tom. La tasse est encore tiède. On dit merci. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le ballon rouge et Tom. Une abeille bourdonne loin. On attend un petit moment. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3614,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi Léa, après le ballon rouge. Un pigeon roucoule. Sara touche Léa tout doucement. Maman dit : je suis là. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+          <t>Sara a choisi Léa, après le ballon rouge. Un pigeon roucoule. Sara touche Léa tout doucement. Je suis là. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3752,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Léa, après le ballon rouge. Un pigeon roucoule. Sara touche Léa tout doucement.
+maman|Je suis là.
+narrateur|Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4112,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le ballon rouge et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le matin à sa place. Sara est près de maman. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse après la sieste à sa place. Sara est près de maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le ballon rouge et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le soir à sa place. Sara est près de maman. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Sami, après le ballon rouge. Le vent fait bouger un rideau. Sami est là. Sara pose les mains à vue, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le ballon rouge et Sami. Un pigeon roucoule. On essuie une miette. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Sami. La cuillère tinte. On referme un livre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6140,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le ballon rouge et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6307,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6474,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu se renverse. Sara est en colère. Sara s'occupe du seau bleu. Un papillon passe sans bruit. Maman sourit. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6655,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le seau bleu.</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6828,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6837,6 +7021,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7001,6 +7190,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Tom, après le seau bleu. Il y a des miettes sur la table. Sara attend près de Tom. Elle ne prend pas de force. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le seau bleu et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le matin à sa place. Sara est près de maman. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le seau bleu et Tom. Le banc est tiède. On se tait une seconde. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse après la sieste à sa place. Sara est près de maman. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le seau bleu et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Léa, après le seau bleu. Un chat miaule une seule fois. On parle de Léa. Sara écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le seau bleu et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le seau bleu et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le seau bleu et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Sami, après le seau bleu. Le vent sent la mer. Près de Sami, Sara prend le temps. Pas de course. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10130,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
+          <t>Sara rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10268,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le seau bleu et Sami. Une plume vole. On range les chaussures. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi.
+narrateur|Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10437,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10175,7 +10466,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. On se serre un peu.</t>
+          <t>Sara rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10313,6 +10604,12 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le seau bleu et Sami. Le pain croustille. On met le doudou près de soi. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10772,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10499,7 +10801,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Maman dit : je t'ai entendu. Papa aussi. On rentre.</t>
+          <t>Sara rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Je t'ai entendu. Papa aussi. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10637,6 +10939,12 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le seau bleu et Sami. La laine du doudou est douce. On écoute le cœur, tout doux. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.
+maman|Je t'ai entendu. Papa aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11107,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11274,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou glisse sous le canapé. Sara est en colère. Voilà le doudou. L'eau fait un tout petit bruit. Sara pose les pieds par terre, près de maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11137,6 +11455,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le doudou.</t>
         </is>
       </c>
     </row>
@@ -11305,6 +11628,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11493,6 +11821,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11657,6 +11990,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Tom, après le doudou. La pomme est croquante. Tom est là. Sara pose les mains à vue, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12181,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12348,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le doudou et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara quitte ce moment et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12515,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12682,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le doudou et Tom. Le train souffle au loin. On pose le sac. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12849,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13016,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le doudou et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara nomme encore le mot, tout bas. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13183,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13350,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Léa, après le doudou. Un ruisseau chante tout bas. Avec Léa, Sara ralentit. Elle écoute maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13541,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13708,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le doudou et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara quitte ce moment et va vers maman. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13875,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14042,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le doudou et Léa. Le bois de la table est lisse. On attend la réponse. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14209,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14376,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le doudou et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara nomme encore le mot, tout bas. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14543,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14710,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi Sami, après le doudou. Une goutte de pluie sèche déjà. On parle de Sami. Sara écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14901,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15068,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin, après le doudou et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara range le matin un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15235,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15402,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste, après le doudou et Sami. La clochette de la porte tinte. On dit stop, tout clair. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15569,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15736,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir, après le doudou et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15903,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15504,6 +15957,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-005.xlsx
+++ b/stories/arbres/TREE-EMO-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Dans le salon, Sara construisait une tour. La tour tombe. Un frère a bougé trop près. Le visage de Sara devient chaud. Maman est sur le canapé. Papa rentre des courses. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Le ballon rouge roule trop loin. Sara est en colère. Voici le ballon rouge. La couverture est toute douce. Sara s'approche, sans courir. Papa n'est pas loin. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le ballon rouge.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Sara a choisi Tom, après le ballon rouge. Une goutte de pluie sèche déjà. Tom reste à sa place. Sara aussi. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2755,6 +2768,7 @@
           <t>narrateur|Sara rejoint le matin, après le ballon rouge et Tom. La tasse est encore tiède. On dit merci. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3104,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Tom. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3272,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3440,7 @@
           <t>narrateur|Sara rejoint le soir, après le ballon rouge et Tom. Une abeille bourdonne loin. On attend un petit moment. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3608,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
 narrateur|Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4117,6 +4138,7 @@
           <t>narrateur|Sara rejoint le matin, après le ballon rouge et Léa. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le matin à sa place. Sara est près de maman. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4474,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Léa. La fenêtre tremble un tout petit peu. On sourit un peu. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse après la sieste à sa place. Sara est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4810,7 @@
           <t>narrateur|Sara rejoint le soir, après le ballon rouge et Léa. Ça sent le savon de maman. On boit une gorgée d'eau. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le soir à sa place. Sara est près de maman. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4978,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5146,7 @@
           <t>narrateur|Sara a choisi Sami, après le ballon rouge. Le vent fait bouger un rideau. Sami est là. Sara pose les mains à vue, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5310,6 +5338,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5477,6 +5506,7 @@
           <t>narrateur|Sara rejoint le matin, après le ballon rouge et Sami. Un pigeon roucoule. On essuie une miette. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5842,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le ballon rouge et Sami. La cuillère tinte. On referme un livre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6178,7 @@
           <t>narrateur|Sara rejoint le soir, après le ballon rouge et Sami. Le ballon est un peu poudreux. On pose un jouet à sa place. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6346,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
           <t>narrateur|Le seau bleu se renverse. Sara est en colère. Sara s'occupe du seau bleu. Un papillon passe sans bruit. Maman sourit. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6662,6 +6698,7 @@
           <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le seau bleu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6833,6 +6870,7 @@
           <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Sara a choisi Tom, après le seau bleu. Il y a des miettes sur la table. Sara attend près de Tom. Elle ne prend pas de force. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Sara rejoint le matin, après le seau bleu et Tom. Une goutte de pluie sèche déjà. On marche tout doucement. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse le matin à sa place. Sara est près de maman. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le seau bleu et Tom. Le banc est tiède. On se tait une seconde. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. On laisse après la sieste à sa place. Sara est près de maman. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Sara rejoint le soir, après le seau bleu et Tom. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Sara a choisi Léa, après le seau bleu. Un chat miaule une seule fois. On parle de Léa. Sara écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Sara rejoint le matin, après le seau bleu et Léa. Une feuille tourne et tombe. On s'assoit près de l'adulte. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le seau bleu et Léa. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Sara rejoint le soir, après le seau bleu et Léa. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Sara a choisi Sami, après le seau bleu. Le vent sent la mer. Près de Sami, Sara prend le temps. Pas de course. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10275,6 +10332,7 @@
 narrateur|Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10442,6 +10500,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10610,6 +10669,7 @@
 maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10777,6 +10837,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10945,6 +11006,7 @@
 maman|Je t'ai entendu. Papa aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11112,6 +11174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11279,6 +11342,7 @@
           <t>narrateur|Le doudou glisse sous le canapé. Sara est en colère. Voilà le doudou. L'eau fait un tout petit bruit. Sara pose les pieds par terre, près de maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11462,6 +11526,7 @@
           <t>narrateur|Sara a le visage chaud. Que fait-on ? Avec le doudou.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11633,6 +11698,7 @@
           <t>narrateur|Oui. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11828,6 +11894,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11995,6 +12062,7 @@
           <t>narrateur|Sara a choisi Tom, après le doudou. La pomme est croquante. Tom est là. Sara pose les mains à vue, loin de l'autre. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12186,6 +12254,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12353,6 +12422,7 @@
           <t>narrateur|Sara rejoint le matin, après le doudou et Tom. Un galet est lisse dans la main. On secoue les mains, loin. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara quitte ce moment et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12520,6 +12590,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12687,6 +12758,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le doudou et Tom. Le train souffle au loin. On pose le sac. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12854,6 +12926,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13021,6 +13094,7 @@
           <t>narrateur|Sara rejoint le soir, après le doudou et Tom. Une vache meugle, loin. On dit le mot de l'émotion. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara nomme encore le mot, tout bas. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13188,6 +13262,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13430,7 @@
           <t>narrateur|Sara a choisi Léa, après le doudou. Un ruisseau chante tout bas. Avec Léa, Sara ralentit. Elle écoute maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13546,6 +13622,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13713,6 +13790,7 @@
           <t>narrateur|Sara rejoint le matin, après le doudou et Léa. Un grillon chante, tout petit. On invite d'une petite voix. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara quitte ce moment et va vers maman. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13880,6 +13958,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14047,6 +14126,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le doudou et Léa. Le bois de la table est lisse. On attend la réponse. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara serre la main de maman, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14214,6 +14294,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14381,6 +14462,7 @@
           <t>narrateur|Sara rejoint le soir, après le doudou et Léa. Une goutte tombe dans l'évier. On propose une autre idée. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14548,6 +14630,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14715,6 +14798,7 @@
           <t>narrateur|Sara a choisi Sami, après le doudou. Une goutte de pluie sèche déjà. On parle de Sami. Sara écoute jusqu'au bout. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14906,6 +14990,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15073,6 +15158,7 @@
           <t>narrateur|Sara rejoint le matin, après le doudou et Sami. Le toboggan est un peu froid. On va vers papa ou maman. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara range le matin un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15240,6 +15326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15407,6 +15494,7 @@
           <t>narrateur|Sara rejoint après la sieste, après le doudou et Sami. La clochette de la porte tinte. On dit stop, tout clair. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara boit une gorgée. Elle se sent plus légère. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15574,6 +15662,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15741,6 +15830,7 @@
           <t>narrateur|Sara rejoint le soir, après le doudou et Sami. Ça sent le thym du jardin. On s'éloigne d'un pas. Sara se sent en colère. Le visage est chaud. Les mains restent loin de l'autre. Sara s'éloigne. Elle souffle. Elle va vers un adulte, vers maman. Sara dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15908,6 +15998,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15926,7 +16017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15964,6 +16055,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15978,7 +16083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16165,6 +16270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
